--- a/4.2.1 кольца ньютона/2026/измерения.xlsx
+++ b/4.2.1 кольца ньютона/2026/измерения.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14750" windowHeight="7260"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14750" windowHeight="7260" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="желтый_темные кольца" sheetId="1" r:id="rId1"/>
-    <sheet name="биения" sheetId="2" r:id="rId2"/>
-    <sheet name="калибровка" sheetId="3" r:id="rId3"/>
+    <sheet name="желтый темные кольца" sheetId="1" r:id="rId1"/>
+    <sheet name="желтый темные светлые" sheetId="4" r:id="rId2"/>
+    <sheet name="биения" sheetId="2" r:id="rId3"/>
+    <sheet name="калибровка" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>n, номер кольца</t>
   </si>
@@ -56,6 +57,24 @@
   </si>
   <si>
     <t>оценка: фокус 5 см</t>
+  </si>
+  <si>
+    <t>центр</t>
+  </si>
+  <si>
+    <t>погрешность</t>
+  </si>
+  <si>
+    <t>r_d_min</t>
+  </si>
+  <si>
+    <t>r_d_max</t>
+  </si>
+  <si>
+    <t>r_l_min</t>
+  </si>
+  <si>
+    <t>r_l_max</t>
   </si>
 </sst>
 </file>
@@ -375,15 +394,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,8 +413,14 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-15</v>
       </c>
@@ -404,8 +430,16 @@
       <c r="C2">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <f>AVERAGE(B2:C33)</f>
+        <v>593.61290322580646</v>
+      </c>
+      <c r="F2">
+        <f>SQRT(COUNT(B2:C33) * 0.5*0.5)/COUNT(B2:C33)</f>
+        <v>6.3500063500095252E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-14</v>
       </c>
@@ -416,7 +450,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-13</v>
       </c>
@@ -427,7 +461,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-12</v>
       </c>
@@ -438,7 +472,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>-11</v>
       </c>
@@ -449,7 +483,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>-10</v>
       </c>
@@ -460,7 +494,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>-9</v>
       </c>
@@ -471,7 +505,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-8</v>
       </c>
@@ -482,7 +516,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-7</v>
       </c>
@@ -493,7 +527,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-6</v>
       </c>
@@ -504,7 +538,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-5</v>
       </c>
@@ -515,7 +549,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-4</v>
       </c>
@@ -526,7 +560,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-3</v>
       </c>
@@ -537,7 +571,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-2</v>
       </c>
@@ -548,7 +582,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-1</v>
       </c>
@@ -762,13 +796,554 @@
         <v>1118</v>
       </c>
       <c r="D33" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>-15</v>
+      </c>
+      <c r="B2">
+        <v>74</v>
+      </c>
+      <c r="C2">
+        <v>67</v>
+      </c>
+      <c r="D2">
+        <v>87</v>
+      </c>
+      <c r="E2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>-14</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>87</v>
+      </c>
+      <c r="D3">
+        <v>103</v>
+      </c>
+      <c r="E3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>-13</v>
+      </c>
+      <c r="B4">
+        <v>110</v>
+      </c>
+      <c r="C4">
+        <v>103</v>
+      </c>
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>-12</v>
+      </c>
+      <c r="B5">
+        <v>128</v>
+      </c>
+      <c r="C5">
+        <v>120</v>
+      </c>
+      <c r="D5">
+        <v>141</v>
+      </c>
+      <c r="E5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>-11</v>
+      </c>
+      <c r="B6">
+        <v>145</v>
+      </c>
+      <c r="C6">
+        <v>141</v>
+      </c>
+      <c r="D6">
+        <v>156</v>
+      </c>
+      <c r="E6">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>-10</v>
+      </c>
+      <c r="B7">
+        <v>164</v>
+      </c>
+      <c r="C7">
+        <v>156</v>
+      </c>
+      <c r="D7">
+        <v>174</v>
+      </c>
+      <c r="E7">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>-9</v>
+      </c>
+      <c r="B8">
+        <v>186</v>
+      </c>
+      <c r="C8">
+        <v>174</v>
+      </c>
+      <c r="D8">
+        <v>196</v>
+      </c>
+      <c r="E8">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>-8</v>
+      </c>
+      <c r="B9">
+        <v>206</v>
+      </c>
+      <c r="C9">
+        <v>196</v>
+      </c>
+      <c r="D9">
+        <v>218</v>
+      </c>
+      <c r="E9">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>-7</v>
+      </c>
+      <c r="B10">
+        <v>229</v>
+      </c>
+      <c r="C10">
+        <v>218</v>
+      </c>
+      <c r="D10">
+        <v>241</v>
+      </c>
+      <c r="E10">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>-6</v>
+      </c>
+      <c r="B11">
+        <v>249</v>
+      </c>
+      <c r="C11">
+        <v>241</v>
+      </c>
+      <c r="D11">
+        <v>262</v>
+      </c>
+      <c r="E11">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>-5</v>
+      </c>
+      <c r="B12">
+        <v>277</v>
+      </c>
+      <c r="C12">
+        <v>262</v>
+      </c>
+      <c r="D12">
+        <v>291</v>
+      </c>
+      <c r="E12">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>-4</v>
+      </c>
+      <c r="B13">
+        <v>304</v>
+      </c>
+      <c r="C13">
+        <v>291</v>
+      </c>
+      <c r="D13">
+        <v>324</v>
+      </c>
+      <c r="E13">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>-3</v>
+      </c>
+      <c r="B14">
+        <v>336</v>
+      </c>
+      <c r="C14">
+        <v>324</v>
+      </c>
+      <c r="D14">
+        <v>359</v>
+      </c>
+      <c r="E14">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>-2</v>
+      </c>
+      <c r="B15">
+        <v>373</v>
+      </c>
+      <c r="C15">
+        <v>359</v>
+      </c>
+      <c r="D15">
+        <v>400</v>
+      </c>
+      <c r="E15">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>-1</v>
+      </c>
+      <c r="B16">
+        <v>416</v>
+      </c>
+      <c r="C16">
+        <v>400</v>
+      </c>
+      <c r="D16">
+        <v>450</v>
+      </c>
+      <c r="E16">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1">
+        <v>769</v>
+      </c>
+      <c r="C17" s="1">
+        <v>790</v>
+      </c>
+      <c r="D17" s="1">
+        <v>735</v>
+      </c>
+      <c r="E17" s="1">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1">
+        <v>815</v>
+      </c>
+      <c r="C18" s="1">
+        <v>829</v>
+      </c>
+      <c r="D18" s="1">
+        <v>790</v>
+      </c>
+      <c r="E18" s="1">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1">
+        <v>851</v>
+      </c>
+      <c r="C19" s="1">
+        <v>861</v>
+      </c>
+      <c r="D19" s="1">
+        <v>829</v>
+      </c>
+      <c r="E19" s="1">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1">
+        <v>884</v>
+      </c>
+      <c r="C20" s="1">
+        <v>893</v>
+      </c>
+      <c r="D20" s="1">
+        <v>861</v>
+      </c>
+      <c r="E20" s="1">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1">
+        <v>910</v>
+      </c>
+      <c r="C21" s="1">
+        <v>922</v>
+      </c>
+      <c r="D21" s="1">
+        <v>893</v>
+      </c>
+      <c r="E21" s="1">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1">
+        <v>938</v>
+      </c>
+      <c r="C22" s="1">
+        <v>941</v>
+      </c>
+      <c r="D22" s="1">
+        <v>922</v>
+      </c>
+      <c r="E22" s="1">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23" s="1">
+        <v>957</v>
+      </c>
+      <c r="C23" s="1">
+        <v>966</v>
+      </c>
+      <c r="D23" s="1">
+        <v>941</v>
+      </c>
+      <c r="E23" s="1">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1">
+        <v>979</v>
+      </c>
+      <c r="C24" s="1">
+        <v>992</v>
+      </c>
+      <c r="D24" s="1">
+        <v>966</v>
+      </c>
+      <c r="E24" s="1">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1015</v>
+      </c>
+      <c r="D25" s="1">
+        <v>992</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1025</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1033</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1015</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>11</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1042</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1050</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1033</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>12</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1062</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1068</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1050</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1077</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1083</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1068</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1097</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1103</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1083</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>15</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1117</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1118</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1103</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -791,20 +1366,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1">
+        <f>1116-93</f>
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
